--- a/Result/profitability/2331.xlsx
+++ b/Result/profitability/2331.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.14</v>
       </c>
       <c r="M2" t="n">
-        <v>0.17</v>
+        <v>0.2275</v>
       </c>
       <c r="N2" t="n">
-        <v>9.845000000000001</v>
+        <v>9.403749999999999</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.15</v>
       </c>
       <c r="M3" t="n">
-        <v>0.195</v>
+        <v>0.27625</v>
       </c>
       <c r="N3" t="n">
-        <v>9.3775</v>
+        <v>9.546249999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>0.23625</v>
+        <v>0.16</v>
       </c>
       <c r="N4" t="n">
-        <v>9.307499999999999</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.11</v>
       </c>
       <c r="M5" t="n">
-        <v>0.09500000000000003</v>
+        <v>0.15875</v>
       </c>
       <c r="N5" t="n">
-        <v>7.985</v>
+        <v>7.66625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.12875</v>
+        <v>0.11625</v>
       </c>
       <c r="N6" t="n">
-        <v>7.8</v>
+        <v>7.57625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>0.115</v>
+        <v>0.17</v>
       </c>
       <c r="N7" t="n">
-        <v>7.75125</v>
+        <v>7.48625</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1276,10 +1276,10 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.23</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1475</v>
+        <v>0.185</v>
       </c>
       <c r="N8" t="n">
-        <v>7.6275</v>
+        <v>7.515</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>0.11125</v>
       </c>
       <c r="N10" t="n">
-        <v>7.42875</v>
+        <v>7.428749999999999</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2331</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5749</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5301</v>
+      </c>
+      <c r="E75" t="n">
+        <v>448</v>
+      </c>
+      <c r="F75" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="G75" t="n">
+        <v>13</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>0.22%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>225</v>
+      </c>
+      <c r="J75" t="n">
+        <v>238</v>
+      </c>
+      <c r="K75" t="n">
+        <v>231</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.20375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X75" t="n">
+        <v>2.727272727272727</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.8999999999999995</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1035673187571922</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-5.1</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-2.55</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.246615087040619</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
